--- a/branches/release/v2027.0.0-ballot/CodeSystem-mii-cs-kardio-supplement-snomedct.xlsx
+++ b/branches/release/v2027.0.0-ballot/CodeSystem-mii-cs-kardio-supplement-snomedct.xlsx
@@ -150,10 +150,10 @@
     <t>73544002|Operation on heart valve|:{260507000|Access|=260519008|Transcatheter approach|}</t>
   </si>
   <si>
-    <t>64572001:{116676008=50960005,47429007=131148009,42752001=789750003,246112005=24484000}</t>
-  </si>
-  <si>
-    <t>64572001|Disease|:{116676008|Associated morphology|=50960005|Hemorrhage|,47429007|Associated with|=131148009|Bleeding|,42752001|Due to|=789750003|Spontaneous event|,246112005|Severity|=24484000|Severe|}</t>
+    <t>131148009:{42752001=789750003,246112005=24484000}</t>
+  </si>
+  <si>
+    <t>131148009|Bleeding|:{42752001|Due to|=789750003|Spontaneous event|,246112005|Severity|=24484000|Severe|}</t>
   </si>
 </sst>
 </file>
